--- a/generated/sources/systems/planning/FW26_merch_plan_OTB_v5.xlsx
+++ b/generated/sources/systems/planning/FW26_merch_plan_OTB_v5.xlsx
@@ -72,7 +72,7 @@
             <rFont val="Arial"/>
             <family val="2"/>
           </rPr>
-          <t xml:space="preserve">Include riassortimento MAIRE nero 420 pz (PO 4500218734) - ETA 02/10 (era 25/9)</t>
+          <t xml:space="preserve">Include riassortimento AUREA nero 420 pz (PO 4500218734) - ETA 02/10 (era 25/9)</t>
         </r>
       </text>
       <mc:AlternateContent>
@@ -489,7 +489,7 @@
             <rFont val="Arial"/>
             <family val="2"/>
           </rPr>
-          <t xml:space="preserve">Polaris: piano CN/HK ok. ILVARO rosa nessun upside previsto</t>
+          <t xml:space="preserve">Astra: piano CN/HK ok. IRIDIA rosa nessun upside previsto</t>
         </r>
       </text>
       <mc:AlternateContent>
@@ -779,7 +779,7 @@
     <t xml:space="preserve">campagna FW26 US/UK da 15/9 (+ agenzia stima +20%?)</t>
   </si>
   <si>
-    <t xml:space="preserve">Genius Polaris + Cina forte</t>
+    <t xml:space="preserve">Couture Astra + Cina forte</t>
   </si>
   <si>
     <t xml:space="preserve">Categoria</t>
@@ -809,19 +809,19 @@
     <t xml:space="preserve">Bottoms</t>
   </si>
   <si>
-    <t xml:space="preserve">Polaris (Genius)</t>
+    <t xml:space="preserve">Astra (Couture)</t>
   </si>
   <si>
-    <t xml:space="preserve">Piano EU = profilo Genius drop 2025 (CN/HK), fattore 1.0</t>
+    <t xml:space="preserve">Piano EU = profilo Couture drop 2025 (CN/HK), fattore 1.0</t>
   </si>
   <si>
     <t xml:space="preserve">da rivedere dopo lancio 24/9</t>
   </si>
   <si>
-    <t xml:space="preserve">ILVARO</t>
+    <t xml:space="preserve">IRIDIA</t>
   </si>
   <si>
-    <t xml:space="preserve">analogo BADY x 0,55 (allocazione) / forecast stat. BADY x 0,6</t>
+    <t xml:space="preserve">analogo ARIA x 0,55 (allocazione) / forecast stat. ARIA x 0,6</t>
   </si>
   <si>
     <t xml:space="preserve">colore 510 rosa cipria = 20% buy</t>
